--- a/JsonConverter/ExcelFiles/StageMonsterTableData.xlsx
+++ b/JsonConverter/ExcelFiles/StageMonsterTableData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>몬스터 고유 ID</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>monster_deserteagle_01</t>
+  </si>
+  <si>
+    <t>spawn_monster_stage_3</t>
   </si>
 </sst>
 </file>
@@ -519,10 +522,10 @@
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3"/>
@@ -550,9 +553,15 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
